--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -193,7 +193,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -228,7 +228,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -484,110 +484,44 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>1101</v>
+        <v>1002</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1102</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1103</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1104</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="7" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1105</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1101</v>
-      </c>
-      <c r="E11" s="5">
-        <v>2</v>
-      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C12" s="1">
-        <v>7</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1102</v>
-      </c>
-      <c r="E12" s="5">
-        <v>2</v>
-      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C13" s="1">
-        <v>8</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1103</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2</v>
-      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1104</v>
-      </c>
-      <c r="E14" s="5">
-        <v>2</v>
-      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1105</v>
-      </c>
-      <c r="E15" s="5">
-        <v>2</v>
-      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
